--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487194_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487194_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>C. POLANCO MERINO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4714</v>
+        <v>4.0553</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7227</v>
+        <v>6.626</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7486</v>
+        <v>-2.5707</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2139</v>
+        <v>4.0641</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2052</v>
+        <v>0.8539</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4191</v>
+        <v>3.2102</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9278</v>
+        <v>6.3791</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9103</v>
+        <v>1.3816</v>
       </c>
       <c r="L2" t="n">
-        <v>1.0175</v>
+        <v>4.9974</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7139</v>
+        <v>-2.3149</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1155</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5984</v>
+        <v>-1.7872</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.1231</v>
+        <v>0.772</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7371</v>
+        <v>0.772</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4108</v>
+        <v>-0.1669</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7855</v>
+        <v>0.2469</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6253</v>
+        <v>-0.4138</v>
       </c>
       <c r="V2" t="n">
-        <v>3.9698</v>
+        <v>-0.614</v>
       </c>
       <c r="W2" t="n">
-        <v>4.8696</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8999</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. POLANCO MERINO</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.741</v>
+        <v>3.951</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5258</v>
+        <v>4.1393</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.7848</v>
+        <v>-0.1883</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0641</v>
+        <v>0.2139</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8539</v>
+        <v>-0.2052</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2102</v>
+        <v>0.4191</v>
       </c>
       <c r="J3" t="n">
-        <v>6.3791</v>
+        <v>1.9278</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3816</v>
+        <v>0.9103</v>
       </c>
       <c r="L3" t="n">
-        <v>4.9974</v>
+        <v>1.0175</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3149</v>
+        <v>-1.7139</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-1.1155</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.7872</v>
+        <v>-0.5984</v>
       </c>
       <c r="P3" t="n">
-        <v>0.772</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R3" t="n">
-        <v>0.772</v>
+        <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4812</v>
+        <v>1.8904</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1468</v>
+        <v>1.2021</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.628</v>
+        <v>0.6884</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.614</v>
+        <v>3.9698</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>4.8696</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.614</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.431</v>
+        <v>1.2985</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.7021</v>
+        <v>-1.1826</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1331</v>
+        <v>2.4811</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2788</v>
@@ -766,13 +766,13 @@
         <v>0.965</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9115</v>
+        <v>-0.044</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5354</v>
+        <v>-0.0159</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3761</v>
+        <v>-0.0281</v>
       </c>
       <c r="V4" t="n">
         <v>0.6562</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ALLAS MENESES</t>
+          <t>M. HERRERO CRESPO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9505</v>
+        <v>-0.51</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5423</v>
+        <v>1.9023</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4928</v>
+        <v>-2.4122</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5655</v>
+        <v>3.1722</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9139</v>
+        <v>1.7606</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3484</v>
+        <v>1.4116</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9762</v>
+        <v>3.6388</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3414</v>
+        <v>2.9962</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6348</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5417</v>
+        <v>-0.4666</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2554</v>
+        <v>-1.2356</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2863</v>
+        <v>0.769</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.772</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R5" t="n">
-        <v>0.193</v>
+        <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7151999999999999</v>
+        <v>-0.2033</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8593</v>
+        <v>-0.3552</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1441</v>
+        <v>0.152</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3281</v>
+        <v>-2.1278</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3281</v>
+        <v>1.5138</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-3.6417</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3287</v>
+        <v>-0.948</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9424</v>
+        <v>-0.642</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3863</v>
+        <v>-0.306</v>
       </c>
       <c r="G6" t="n">
         <v>0.4827</v>
@@ -922,13 +922,13 @@
         <v>0.193</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1395</v>
+        <v>0.2413</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0595</v>
+        <v>0.2409</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.08</v>
+        <v>0.0003</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8999</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. HERRERO CRESPO</t>
+          <t>S. MARTINEZ ORTIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.437</v>
+        <v>-1.2231</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0823</v>
+        <v>1.0049</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5193</v>
+        <v>-2.2279</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1722</v>
+        <v>-1.6596</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7606</v>
+        <v>-0.8942</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4116</v>
+        <v>-0.7654</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6388</v>
+        <v>0.5615</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9962</v>
+        <v>-0.0726</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.6341</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4666</v>
+        <v>-2.2211</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2356</v>
+        <v>-0.8216</v>
       </c>
       <c r="O7" t="n">
-        <v>0.769</v>
+        <v>-1.3995</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3511</v>
+        <v>-0.579</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1303</v>
+        <v>0.1157</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1752</v>
+        <v>0.2456</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0449</v>
+        <v>-0.1299</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1278</v>
+        <v>0.8999</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5138</v>
+        <v>2.1278</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.6417</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. MARTINEZ ORTIZ</t>
+          <t>A. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6435</v>
+        <v>-1.5582</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5042</v>
+        <v>0.0416</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1476</v>
+        <v>-1.5999</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6596</v>
+        <v>-0.5655</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8942</v>
+        <v>-0.9139</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7654</v>
+        <v>0.3484</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5615</v>
+        <v>0.9762</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0726</v>
+        <v>0.3414</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6341</v>
+        <v>0.6348</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2211</v>
+        <v>-1.5417</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8216</v>
+        <v>-1.2554</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3995</v>
+        <v>-0.2863</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.579</v>
+        <v>-0.772</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3511</v>
+        <v>0.193</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3047</v>
+        <v>0.1074</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2551</v>
+        <v>0.3586</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0496</v>
+        <v>-0.2512</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8999</v>
+        <v>-0.3281</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1278</v>
+        <v>-0.3281</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1443</v>
+        <v>-2.0838</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.6292</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8736</v>
+        <v>-2.713</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7895</v>
@@ -1156,13 +1156,13 @@
         <v>0.579</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5222</v>
+        <v>0.5827</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4587</v>
+        <v>0.3586</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0634</v>
+        <v>0.2241</v>
       </c>
       <c r="V9" t="n">
         <v>-2.4559</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6042</v>
+        <v>-3.2513</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8604</v>
+        <v>-1.6413</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7438</v>
+        <v>-1.61</v>
       </c>
       <c r="G10" t="n">
         <v>1.3342</v>
@@ -1234,13 +1234,13 @@
         <v>0.772</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2618</v>
+        <v>1.6148</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8289</v>
+        <v>1.048</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4329</v>
+        <v>0.5668</v>
       </c>
       <c r="V10" t="n">
         <v>-3.1122</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8446</v>
+        <v>-3.4451</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3274</v>
+        <v>-4.0081</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4827</v>
+        <v>0.5631</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9681</v>
@@ -1312,13 +1312,13 @@
         <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5255</v>
+        <v>-0.1259</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4759</v>
+        <v>-0.1566</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0496</v>
+        <v>0.0307</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3094</v>
+        <v>-3.714700000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>6.274299999999999</v>
+        <v>6.8693</v>
       </c>
       <c r="F12" t="n">
         <v>-10.5838</v>
@@ -1369,10 +1369,10 @@
         <v>4.2422</v>
       </c>
       <c r="L12" t="n">
-        <v>8.332800000000001</v>
+        <v>8.332799999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.569300000000002</v>
+        <v>-8.5693</v>
       </c>
       <c r="N12" t="n">
         <v>-5.5774</v>
@@ -1390,13 +1390,13 @@
         <v>8.685300000000002</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4173</v>
+        <v>4.0122</v>
       </c>
       <c r="T12" t="n">
-        <v>2.578099999999999</v>
+        <v>3.173</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8391000000000001</v>
+        <v>0.8392999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-4.012</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.9016</v>
+        <v>7.0546</v>
       </c>
       <c r="E13" t="n">
-        <v>6.6901</v>
+        <v>6.7903</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2115</v>
+        <v>0.2644</v>
       </c>
       <c r="G13" t="n">
         <v>3.2899</v>
@@ -1468,13 +1468,13 @@
         <v>1.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0529</v>
+        <v>0.1001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1956</v>
+        <v>-0.0955</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1427</v>
+        <v>0.1956</v>
       </c>
       <c r="V13" t="n">
         <v>2.6996</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9671</v>
+        <v>4.2695</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9908</v>
+        <v>5.892</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0237</v>
+        <v>-1.6225</v>
       </c>
       <c r="G14" t="n">
         <v>-0.7261</v>
@@ -1546,13 +1546,13 @@
         <v>2.7021</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.3016</v>
+        <v>-0.9991</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3391</v>
+        <v>-0.4379</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9624</v>
+        <v>-0.5612</v>
       </c>
       <c r="V14" t="n">
         <v>4.2576</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9883</v>
+        <v>2.1016</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9159</v>
+        <v>1.8158</v>
       </c>
       <c r="F15" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.2859</v>
       </c>
       <c r="G15" t="n">
         <v>2.1023</v>
@@ -1624,13 +1624,13 @@
         <v>2.7021</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3649</v>
+        <v>0.4782</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2935</v>
+        <v>0.1934</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0713</v>
+        <v>0.2849</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2859</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. REYES ABAD</t>
+          <t>A. LOPEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9593</v>
+        <v>0.5653</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0725</v>
+        <v>1.5108</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1132</v>
+        <v>-0.9456</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.1369</v>
+        <v>-0.0915</v>
       </c>
       <c r="H16" t="n">
-        <v>0.737</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.8739</v>
+        <v>-0.9247</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2247</v>
+        <v>0.4888</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4385</v>
+        <v>0.9936</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2138</v>
+        <v>-0.5048</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3616</v>
+        <v>-0.5802</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7015</v>
+        <v>-0.1604</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6601</v>
+        <v>-0.4199</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7021</v>
+        <v>1.158</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7021</v>
+        <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5189</v>
+        <v>-0.1752</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6042</v>
+        <v>-0.2059</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0853</v>
+        <v>0.0307</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1248</v>
+        <v>-0.3261</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2436</v>
+        <v>1.228</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3684</v>
+        <v>-1.5541</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. LOPEZ FERNANDEZ</t>
+          <t>A. REYES ABAD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3445</v>
+        <v>0.4917</v>
       </c>
       <c r="E17" t="n">
-        <v>1.611</v>
+        <v>0.4717</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2665</v>
+        <v>0.02</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0915</v>
+        <v>-2.1369</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.737</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9247</v>
+        <v>-2.8739</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4888</v>
+        <v>0.2247</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9936</v>
+        <v>1.4385</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5048</v>
+        <v>-1.2138</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5802</v>
+        <v>-2.3616</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1604</v>
+        <v>-0.7015</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4199</v>
+        <v>-1.6601</v>
       </c>
       <c r="P17" t="n">
-        <v>1.158</v>
+        <v>2.7021</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.158</v>
+        <v>2.7021</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3959</v>
+        <v>0.0512</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1057</v>
+        <v>0.0034</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2902</v>
+        <v>0.0479</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3261</v>
+        <v>-0.1248</v>
       </c>
       <c r="W17" t="n">
-        <v>1.228</v>
+        <v>0.2436</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5541</v>
+        <v>-0.3684</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2394</v>
+        <v>-0.2196</v>
       </c>
       <c r="E18" t="n">
-        <v>1.186</v>
+        <v>1.2861</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4255</v>
+        <v>-1.5058</v>
       </c>
       <c r="G18" t="n">
         <v>0.6706</v>
@@ -1858,13 +1858,13 @@
         <v>0.386</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0483</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1785</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1104</v>
+        <v>0.0301</v>
       </c>
       <c r="V18" t="n">
         <v>-1.228</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. KEITH CAMARA</t>
+          <t>D. RUIZ RUIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.328</v>
+        <v>-0.3336</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7942</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4661</v>
+        <v>-0.2552</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2681</v>
+        <v>-0.4204</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1956</v>
+        <v>-0.0134</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4637</v>
+        <v>-0.407</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5491</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2381</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3109</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.281</v>
+        <v>-0.4204</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4338</v>
+        <v>-0.0134</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1528</v>
+        <v>-0.407</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3511</v>
+        <v>0.193</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3511</v>
+        <v>0.193</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8169999999999999</v>
+        <v>-0.4343</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7549</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0621</v>
+        <v>-0.3559</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.228</v>
+        <v>0.3281</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.228</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. RUIZ RUIZ</t>
+          <t>D. KEITH CAMARA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4605</v>
+        <v>-0.8628</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1785</v>
+        <v>-1.1948</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.282</v>
+        <v>0.332</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4204</v>
+        <v>-1.2681</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0134</v>
+        <v>0.1956</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.407</v>
+        <v>-1.4637</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-1.5491</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.2381</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.3109</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4204</v>
+        <v>0.281</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0134</v>
+        <v>0.4338</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.407</v>
+        <v>-0.1528</v>
       </c>
       <c r="P20" t="n">
-        <v>0.193</v>
+        <v>1.3511</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.193</v>
+        <v>1.3511</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5612</v>
+        <v>0.2822</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1785</v>
+        <v>0.3543</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3827</v>
+        <v>-0.0721</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3281</v>
+        <v>-1.228</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3281</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6349</v>
+        <v>-3.6081</v>
       </c>
       <c r="E21" t="n">
         <v>-3.597</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0379</v>
+        <v>-0.0111</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1799</v>
@@ -2092,13 +2092,13 @@
         <v>1.3511</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4726</v>
+        <v>-0.4458</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1057</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3669</v>
+        <v>-0.3401</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3684</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1885</v>
+        <v>-3.8141</v>
       </c>
       <c r="E22" t="n">
         <v>-2.3129</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8756</v>
+        <v>-1.5012</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2455</v>
@@ -2170,13 +2170,13 @@
         <v>1.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2658</v>
+        <v>-0.8913</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3886</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8772</v>
+        <v>-0.5027</v>
       </c>
       <c r="V22" t="n">
         <v>0.2878</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.309499999999999</v>
+        <v>5.644499999999999</v>
       </c>
       <c r="E23" t="n">
         <v>10.5837</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.2744</v>
+        <v>-4.9391</v>
       </c>
       <c r="G23" t="n">
         <v>-4.005599999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3352</v>
+        <v>1.335200000000001</v>
       </c>
       <c r="I23" t="n">
         <v>-5.3407</v>
@@ -2236,10 +2236,10 @@
         <v>-4.2422</v>
       </c>
       <c r="O23" t="n">
-        <v>-8.332799999999999</v>
+        <v>-8.332800000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>7.720299999999998</v>
+        <v>7.7203</v>
       </c>
       <c r="Q23" t="n">
         <v>-8.6852</v>
@@ -2248,13 +2248,13 @@
         <v>16.4057</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.4173</v>
+        <v>-2.0823</v>
       </c>
       <c r="T23" t="n">
         <v>-0.8391</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.5782</v>
+        <v>-1.2428</v>
       </c>
       <c r="V23" t="n">
         <v>4.011900000000001</v>
